--- a/branches/cpg-guidance/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
+++ b/branches/cpg-guidance/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>urn:uuid:5443da66-91e5-42ea-aeb4-b00b98188e47</t>
+    <t>urn:uuid:5b4c92c6-8415-4e2f-81b2-68fbd92f5898</t>
   </si>
   <si>
     <t>Version</t>

--- a/branches/cpg-guidance/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
+++ b/branches/cpg-guidance/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>urn:uuid:5b4c92c6-8415-4e2f-81b2-68fbd92f5898</t>
+    <t>urn:uuid:244927b3-1cf6-4a3b-962a-73844a510754</t>
   </si>
   <si>
     <t>Version</t>

--- a/branches/cpg-guidance/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
+++ b/branches/cpg-guidance/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>urn:uuid:244927b3-1cf6-4a3b-962a-73844a510754</t>
+    <t>urn:uuid:84f03d43-23c7-4cca-8453-4a2bd7932753</t>
   </si>
   <si>
     <t>Version</t>
